--- a/public/database/job_performance_0519.xlsx
+++ b/public/database/job_performance_0519.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27428" windowHeight="13234"/>
+    <workbookView windowWidth="26580" windowHeight="13234"/>
   </bookViews>
   <sheets>
     <sheet name="1-卸车岗绩效偏高明细" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <t>中心</t>
   </si>
   <si>
-    <t>目标值</t>
+    <t>岗位</t>
   </si>
   <si>
     <t>当月人均日绩效</t>
@@ -660,7 +660,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2032,10 +2032,10 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
         <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>42</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -2061,10 +2061,10 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" t="s">
         <v>49</v>
-      </c>
-      <c r="D25" t="s">
-        <v>26</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>

--- a/public/database/job_performance_0519.xlsx
+++ b/public/database/job_performance_0519.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>数据日期</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>岗位</t>
+  </si>
+  <si>
+    <t>目标值</t>
   </si>
   <si>
     <t>当月人均日绩效</t>
@@ -1385,22 +1388,25 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customHeight="1" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
         <v>108.7</v>
@@ -1409,27 +1415,27 @@
         <v>13.5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:9">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
         <v>156.6</v>
@@ -1446,19 +1452,19 @@
     </row>
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2">
         <v>171.2</v>
@@ -1475,19 +1481,19 @@
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>132.1</v>
@@ -1504,19 +1510,19 @@
     </row>
     <row r="6" customHeight="1" spans="1:9">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="2">
         <v>108.1</v>
@@ -1525,27 +1531,27 @@
         <v>22.3</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2">
         <v>114.8</v>
@@ -1554,27 +1560,27 @@
         <v>14.8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2">
         <v>135.3</v>
@@ -1591,19 +1597,19 @@
     </row>
     <row r="9" customHeight="1" spans="1:9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2">
         <v>81.1</v>
@@ -1612,27 +1618,27 @@
         <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:9">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2">
         <v>108.9</v>
@@ -1641,27 +1647,27 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:9">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2">
         <v>144.6</v>
@@ -1678,19 +1684,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:9">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2">
         <v>75.7</v>
@@ -1699,27 +1705,27 @@
         <v>23</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
         <v>119.9</v>
@@ -1736,19 +1742,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="2">
         <v>101</v>
@@ -1765,19 +1771,19 @@
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="2">
         <v>89.6</v>
@@ -1786,27 +1792,27 @@
         <v>29.4</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="2">
         <v>88.2</v>
@@ -1815,27 +1821,27 @@
         <v>27.5</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2">
         <v>70.2</v>
@@ -1844,27 +1850,27 @@
         <v>21.7</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" s="2">
         <v>81.1</v>
@@ -1873,27 +1879,27 @@
         <v>13.1</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2">
         <v>90.1</v>
@@ -1902,27 +1908,27 @@
         <v>11.6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" s="2">
         <v>124.7</v>
@@ -1939,19 +1945,19 @@
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2">
         <v>112.8</v>
@@ -1968,19 +1974,19 @@
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" s="2">
         <v>142</v>
@@ -1997,19 +2003,19 @@
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="2">
         <v>70.4</v>
@@ -2018,27 +2024,27 @@
         <v>22.1</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
         <v>29</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
       </c>
       <c r="F24" s="2">
         <v>83</v>
@@ -2047,27 +2053,27 @@
         <v>13.6</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="2">
         <v>113.6</v>
